--- a/wwwroot/assets/template/Author_Template.xlsx
+++ b/wwwroot/assets/template/Author_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASP.NET\WebTruyenTranh\wwwroot\assets\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55DC48CA-634A-4440-82A2-B41E86DBCC3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1716D63-097F-448B-9FF4-A0DC0D69DD17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,9 +25,6 @@
     <t>LIST OF AUTHORS</t>
   </si>
   <si>
-    <t>Export date: 23/01/2026 14:54:27</t>
-  </si>
-  <si>
     <t>Total authors: 3</t>
   </si>
   <si>
@@ -43,9 +40,6 @@
     <t>Gender</t>
   </si>
   <si>
-    <t>Trần Thị B</t>
-  </si>
-  <si>
     <t>1990/03/22</t>
   </si>
   <si>
@@ -55,18 +49,12 @@
     <t>Female</t>
   </si>
   <si>
-    <t>Nguyễn Thị F</t>
-  </si>
-  <si>
     <t>1995/08/30</t>
   </si>
   <si>
     <t>f.nguyen@example.com</t>
   </si>
   <si>
-    <t>Lê Thị H</t>
-  </si>
-  <si>
     <t>1991/04/12</t>
   </si>
   <si>
@@ -77,6 +65,18 @@
   </si>
   <si>
     <t>Vietnam</t>
+  </si>
+  <si>
+    <t>Tran Thi B</t>
+  </si>
+  <si>
+    <t>Nguyen Thi F</t>
+  </si>
+  <si>
+    <t>Le Thi H</t>
+  </si>
+  <si>
+    <t>Export date: 23/09/2026 14:54:27</t>
   </si>
 </sst>
 </file>
@@ -435,7 +435,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -445,7 +445,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -455,70 +455,70 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
         <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
